--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129728053</v>
+        <v>129726755</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489121</v>
+        <v>489150</v>
       </c>
       <c r="R2" t="n">
-        <v>7143491</v>
+        <v>7143488</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,14 +743,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,54 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726755</v>
+        <v>129728053</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,16 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489150</v>
+        <v>489121</v>
       </c>
       <c r="R3" t="n">
-        <v>7143488</v>
+        <v>7143491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +853,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,18 +869,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -916,7 +916,7 @@
         <v>129726756</v>
       </c>
       <c r="B4" t="n">
-        <v>78088</v>
+        <v>78089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129728054</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129726755</v>
+        <v>129728053</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,16 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489150</v>
+        <v>489121</v>
       </c>
       <c r="R2" t="n">
-        <v>7143488</v>
+        <v>7143491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +746,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,28 +762,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129728053</v>
+        <v>129726755</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,19 +835,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489121</v>
+        <v>489150</v>
       </c>
       <c r="R3" t="n">
-        <v>7143491</v>
+        <v>7143488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,14 +874,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,44 +895,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -916,7 +916,7 @@
         <v>129726756</v>
       </c>
       <c r="B4" t="n">
-        <v>78089</v>
+        <v>78094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129728054</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129728053</v>
+        <v>129726755</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489121</v>
+        <v>489150</v>
       </c>
       <c r="R2" t="n">
-        <v>7143491</v>
+        <v>7143488</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,14 +743,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,54 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726755</v>
+        <v>129728053</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,16 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489150</v>
+        <v>489121</v>
       </c>
       <c r="R3" t="n">
-        <v>7143488</v>
+        <v>7143491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +853,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,18 +869,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -916,7 +916,7 @@
         <v>129726756</v>
       </c>
       <c r="B4" t="n">
-        <v>78094</v>
+        <v>78097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129728054</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129726755</v>
+        <v>129728053</v>
       </c>
       <c r="B2" t="n">
         <v>79084</v>
@@ -704,16 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489150</v>
+        <v>489121</v>
       </c>
       <c r="R2" t="n">
-        <v>7143488</v>
+        <v>7143491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +746,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,25 +762,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129728053</v>
+        <v>129726755</v>
       </c>
       <c r="B3" t="n">
         <v>79084</v>
@@ -811,19 +835,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489121</v>
+        <v>489150</v>
       </c>
       <c r="R3" t="n">
-        <v>7143491</v>
+        <v>7143488</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,14 +874,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,44 +895,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728053</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>129726755</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>129726756</v>
       </c>
       <c r="B4" t="n">
-        <v>78097</v>
+        <v>78100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129728054</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129728053</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>129726755</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129728054</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129728053</v>
+        <v>129726755</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489121</v>
+        <v>489150</v>
       </c>
       <c r="R2" t="n">
-        <v>7143491</v>
+        <v>7143488</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,14 +743,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,54 +764,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726755</v>
+        <v>129728053</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,16 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489150</v>
+        <v>489121</v>
       </c>
       <c r="R3" t="n">
-        <v>7143488</v>
+        <v>7143491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +853,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,18 +869,44 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -916,7 +916,7 @@
         <v>129726756</v>
       </c>
       <c r="B4" t="n">
-        <v>78100</v>
+        <v>78101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>129728054</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129728053</v>
+        <v>129726755</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -704,19 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489121</v>
+        <v>489150</v>
       </c>
       <c r="R2" t="n">
-        <v>7143491</v>
+        <v>7143488</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,14 +743,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran.</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,58 +764,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129726755</v>
+        <v>129728053</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -835,16 +811,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489150</v>
+        <v>489121</v>
       </c>
       <c r="R3" t="n">
-        <v>7143488</v>
+        <v>7143491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +853,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,63 +869,92 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129726756</v>
+        <v>129728054</v>
       </c>
       <c r="B4" t="n">
-        <v>78101</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fiskåvattnet Ö, Jmt</t>
+          <t>Västra Fiskåvattnet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489143</v>
+        <v>489129</v>
       </c>
       <c r="R4" t="n">
-        <v>7143493</v>
+        <v>7143512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,19 +984,14 @@
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:28</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en stående död gran med potentiella födosökspår efter tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,28 +1000,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129728054</v>
+        <v>129726756</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>78339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,37 +1055,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västra Fiskåvattnet, Jmt</t>
+          <t>Fiskåvattnet Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>489129</v>
+        <v>489143</v>
       </c>
       <c r="R5" t="n">
-        <v>7143512</v>
+        <v>7143493</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,14 +1112,19 @@
           <t>2025-11-15</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en stående död gran med potentiella födosökspår efter tretåig hackspett.</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,44 +1133,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 50974-2025 artfynd.xlsx
+++ b/artfynd/A 50974-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726755</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728053</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728054</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,8 +1168,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129726756</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>